--- a/output/reports/20260702_保育園欠席分析報告書.xlsx
+++ b/output/reports/20260702_保育園欠席分析報告書.xlsx
@@ -1640,7 +1640,7 @@
           <t>月齢別の平均欠席日数は約0.0～0.0日で推移しており、大きな差は認められなかった。
 低学年の平均欠席日数は約15.0日であり、高学年では約0.0日まで減少した。全体で約15.0日の改善がみられ、進級に伴い欠席日数が減少する傾向が確認された。
 登園開始直後の平均欠席日数は約3.0日であり、登園月数の経過とともに約0.0日まで減少した。全体で約3.0日の改善がみられ、園生活への適応が進むにつれて欠席日数が減少する傾向が確認された。
-登園年数が短い時期の平均欠席日数は約26.0日であり、在園年数の増加とともに約0.0日まで減少した。全体で約26.0日の改善がみられ、園生活への適応や生活習慣の定着に伴い、欠席日数が減少する傾向が確認された。
+登園年数が短い時期の平均欠席日数は約26.0日であり、在園年数の増加とともに約0.0日まで減少した。全体で約26.0日の改善がみられ、園生活への適応に伴い欠席日数が減少する傾向が確認された。
 月別では11月の平均欠席日数が約11.5日と最も高く、季節性による影響が比較的強く現れていることが示唆された。
 月間平均欠席日数は約2.0日から約0.0日へ推移し、全体で約2.0日の減少がみられた。継続的な改善傾向が確認されている。</t>
         </is>
@@ -2229,7 +2229,7 @@
           <t>月齢別の平均欠席日数は約0.0～0.0日で推移しており、大きな差は認められなかった。
 低学年の平均欠席日数は約15.0日であり、高学年では約0.0日まで減少した。全体で約15.0日の改善がみられ、進級に伴い欠席日数が減少する傾向が確認された。
 登園開始直後の平均欠席日数は約3.0日であり、登園月数の経過とともに約0.0日まで減少した。全体で約3.0日の改善がみられ、園生活への適応が進むにつれて欠席日数が減少する傾向が確認された。
-登園年数が短い時期の平均欠席日数は約26.0日であり、在園年数の増加とともに約0.0日まで減少した。全体で約26.0日の改善がみられ、園生活への適応や生活習慣の定着に伴い、欠席日数が減少する傾向が確認された。
+登園年数が短い時期の平均欠席日数は約26.0日であり、在園年数の増加とともに約0.0日まで減少した。全体で約26.0日の改善がみられ、園生活への適応に伴い欠席日数が減少する傾向が確認された。
 月別では11月の平均欠席日数が約11.5日と最も高く、季節性による影響が比較的強く現れていることが示唆された。
 月間平均欠席日数は約2.0日から約0.0日へ推移し、全体で約2.0日の減少がみられた。継続的な改善傾向が確認されている。</t>
         </is>
